--- a/Översikt PARTILLE.xlsx
+++ b/Översikt PARTILLE.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE9"/>
+  <dimension ref="A1:AE10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45008</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>46050</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46050</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 35734-2023</t>
+          <t>A 37747-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45147</v>
+        <v>46279</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -950,13 +950,13 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>5.9</v>
+        <v>2.4</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -980,20 +980,52 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
       </c>
-      <c r="V5" s="2" t="inlineStr"/>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1402/artfynd/A 37747-2026 artfynd.xlsx", "A 37747-2026")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1402/kartor/A 37747-2026 karta.png", "A 37747-2026")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1402/kartor_geotiff/A 37747-2026 georefererad karta.tif", "A 37747-2026")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1402/klagomål/A 37747-2026 FSC-klagomål.docx", "A 37747-2026")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1402/klagomålsmail/A 37747-2026 FSC-klagomål mail.docx", "A 37747-2026")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1402/tillsyn/A 37747-2026 tillsynsbegäran.docx", "A 37747-2026")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1402/tillsynsmail/A 37747-2026 tillsynsbegäran mail.docx", "A 37747-2026")</f>
+        <v/>
+      </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 25251-2025</t>
+          <t>A 6983-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1007,10 +1039,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45800</v>
+        <v>44967</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1022,13 +1054,8 @@
           <t>PARTILLE</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I6" t="n">
-        <v>0.7</v>
+        <v>5.4</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1071,7 +1098,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 6983-2023</t>
+          <t>A 25254-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1085,10 +1112,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44967</v>
+        <v>45800</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1100,8 +1127,13 @@
           <t>PARTILLE</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I7" t="n">
-        <v>5.4</v>
+        <v>0.2</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1144,7 +1176,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 25254-2025</t>
+          <t>A 26074-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1158,10 +1190,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45800</v>
+        <v>45805</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1173,13 +1205,8 @@
           <t>PARTILLE</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I8" t="n">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1219,10 +1246,10 @@
       </c>
       <c r="V8" s="2" t="inlineStr"/>
     </row>
-    <row r="9">
+    <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 26074-2025</t>
+          <t>A 25251-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1236,10 +1263,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45805</v>
+        <v>45800</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1251,8 +1278,13 @@
           <t>PARTILLE</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I9" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1291,6 +1323,79 @@
         <v>0</v>
       </c>
       <c r="V9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 35734-2023</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45147</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>PARTILLE</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt PARTILLE.xlsx
+++ b/Översikt PARTILLE.xlsx
@@ -601,7 +601,7 @@
         <v>45008</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>46050</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46050</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>46279</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 6983-2023</t>
+          <t>A 35734-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44967</v>
+        <v>45147</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1098,7 +1098,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 25254-2025</t>
+          <t>A 25251-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1115,7 +1115,7 @@
         <v>45800</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1176,7 +1176,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 26074-2025</t>
+          <t>A 6983-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1190,10 +1190,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45805</v>
+        <v>44967</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.3</v>
+        <v>5.4</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1249,7 +1249,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 25251-2025</t>
+          <t>A 25254-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1266,7 +1266,7 @@
         <v>45800</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1327,7 +1327,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 35734-2023</t>
+          <t>A 26074-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45147</v>
+        <v>45805</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>5.9</v>
+        <v>1.3</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>

--- a/Översikt PARTILLE.xlsx
+++ b/Översikt PARTILLE.xlsx
@@ -601,7 +601,7 @@
         <v>45008</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>46050</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46050</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>46279</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 35734-2023</t>
+          <t>A 6983-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45147</v>
+        <v>44967</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1098,7 +1098,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 25251-2025</t>
+          <t>A 25254-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1115,7 +1115,7 @@
         <v>45800</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1176,7 +1176,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 6983-2023</t>
+          <t>A 26074-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1190,10 +1190,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44967</v>
+        <v>45805</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>5.4</v>
+        <v>1.3</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1249,7 +1249,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 25254-2025</t>
+          <t>A 25251-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1266,7 +1266,7 @@
         <v>45800</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1327,7 +1327,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 26074-2025</t>
+          <t>A 35734-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45805</v>
+        <v>45147</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.3</v>
+        <v>5.9</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>

--- a/Översikt PARTILLE.xlsx
+++ b/Översikt PARTILLE.xlsx
@@ -601,7 +601,7 @@
         <v>45008</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>46050</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46050</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>46279</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 6983-2023</t>
+          <t>A 35734-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44967</v>
+        <v>45147</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1098,7 +1098,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 25254-2025</t>
+          <t>A 25251-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1115,7 +1115,7 @@
         <v>45800</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1176,7 +1176,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 26074-2025</t>
+          <t>A 6983-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1190,10 +1190,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45805</v>
+        <v>44967</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.3</v>
+        <v>5.4</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1249,7 +1249,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 25251-2025</t>
+          <t>A 25254-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1266,7 +1266,7 @@
         <v>45800</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1327,7 +1327,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 35734-2023</t>
+          <t>A 26074-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45147</v>
+        <v>45805</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>5.9</v>
+        <v>1.3</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>

--- a/Översikt PARTILLE.xlsx
+++ b/Översikt PARTILLE.xlsx
@@ -601,7 +601,7 @@
         <v>45008</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>46050</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46050</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>46279</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 35734-2023</t>
+          <t>A 6983-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45147</v>
+        <v>44967</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1115,7 +1115,7 @@
         <v>45800</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 6983-2023</t>
+          <t>A 35734-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1190,10 +1190,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44967</v>
+        <v>45147</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1266,7 +1266,7 @@
         <v>45800</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>45805</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>

--- a/Översikt PARTILLE.xlsx
+++ b/Översikt PARTILLE.xlsx
@@ -601,7 +601,7 @@
         <v>45008</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>46050</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46050</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>46279</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>44967</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>45800</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>45147</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>45800</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>45805</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>

--- a/Översikt PARTILLE.xlsx
+++ b/Översikt PARTILLE.xlsx
@@ -601,7 +601,7 @@
         <v>45008</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>46050</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46050</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>46279</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>44967</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>45800</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>45147</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>45800</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>45805</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>

--- a/Översikt PARTILLE.xlsx
+++ b/Översikt PARTILLE.xlsx
@@ -601,7 +601,7 @@
         <v>45008</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>46050</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46050</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>46279</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 6983-2023</t>
+          <t>A 25251-2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44967</v>
+        <v>45800</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1054,8 +1054,13 @@
           <t>PARTILLE</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I6" t="n">
-        <v>5.4</v>
+        <v>0.7</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1098,7 +1103,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 25251-2025</t>
+          <t>A 35734-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1112,10 +1117,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45800</v>
+        <v>45147</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1127,13 +1132,8 @@
           <t>PARTILLE</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I7" t="n">
-        <v>0.7</v>
+        <v>5.9</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1176,7 +1176,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 35734-2023</t>
+          <t>A 25254-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1190,10 +1190,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45147</v>
+        <v>45800</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1205,8 +1205,13 @@
           <t>PARTILLE</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I8" t="n">
-        <v>5.9</v>
+        <v>0.2</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1249,7 +1254,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 25254-2025</t>
+          <t>A 26074-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1263,10 +1268,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45800</v>
+        <v>45805</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1278,13 +1283,8 @@
           <t>PARTILLE</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I9" t="n">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1327,7 +1327,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 26074-2025</t>
+          <t>A 6983-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45805</v>
+        <v>44967</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.3</v>
+        <v>5.4</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>

--- a/Översikt PARTILLE.xlsx
+++ b/Översikt PARTILLE.xlsx
@@ -601,7 +601,7 @@
         <v>45008</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>46050</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46050</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>46279</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 25251-2025</t>
+          <t>A 6983-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45800</v>
+        <v>44967</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1054,13 +1054,8 @@
           <t>PARTILLE</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I6" t="n">
-        <v>0.7</v>
+        <v>5.4</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1103,7 +1098,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 35734-2023</t>
+          <t>A 25251-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1117,10 +1112,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45147</v>
+        <v>45800</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1132,8 +1127,13 @@
           <t>PARTILLE</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I7" t="n">
-        <v>5.9</v>
+        <v>0.7</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1176,7 +1176,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 25254-2025</t>
+          <t>A 35734-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1190,10 +1190,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45800</v>
+        <v>45147</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1205,13 +1205,8 @@
           <t>PARTILLE</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I8" t="n">
-        <v>0.2</v>
+        <v>5.9</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1254,7 +1249,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 26074-2025</t>
+          <t>A 25254-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1268,10 +1263,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45805</v>
+        <v>45800</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1283,8 +1278,13 @@
           <t>PARTILLE</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I9" t="n">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1327,7 +1327,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 6983-2023</t>
+          <t>A 26074-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44967</v>
+        <v>45805</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>5.4</v>
+        <v>1.3</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>

--- a/Översikt PARTILLE.xlsx
+++ b/Översikt PARTILLE.xlsx
@@ -601,7 +601,7 @@
         <v>45008</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>46050</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46050</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>46279</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 6983-2023</t>
+          <t>A 35734-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44967</v>
+        <v>45147</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1115,7 +1115,7 @@
         <v>45800</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 35734-2023</t>
+          <t>A 25254-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1190,10 +1190,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45147</v>
+        <v>45800</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1205,8 +1205,13 @@
           <t>PARTILLE</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I8" t="n">
-        <v>5.9</v>
+        <v>0.2</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1249,7 +1254,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 25254-2025</t>
+          <t>A 26074-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1263,10 +1268,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45800</v>
+        <v>45805</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1278,13 +1283,8 @@
           <t>PARTILLE</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I9" t="n">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1327,7 +1327,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 26074-2025</t>
+          <t>A 6983-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45805</v>
+        <v>44967</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.3</v>
+        <v>5.4</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>

--- a/Översikt PARTILLE.xlsx
+++ b/Översikt PARTILLE.xlsx
@@ -601,7 +601,7 @@
         <v>45008</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>46050</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46050</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>46279</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>45147</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>45800</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>45800</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>45805</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>44967</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>

--- a/Översikt PARTILLE.xlsx
+++ b/Översikt PARTILLE.xlsx
@@ -601,7 +601,7 @@
         <v>45008</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>46050</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46050</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>46279</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>45147</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>45800</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>45800</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>45805</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>44967</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>

--- a/Översikt PARTILLE.xlsx
+++ b/Översikt PARTILLE.xlsx
@@ -601,7 +601,7 @@
         <v>45008</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>46050</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46050</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>46279</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 35734-2023</t>
+          <t>A 6983-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45147</v>
+        <v>44967</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1115,7 +1115,7 @@
         <v>45800</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>45800</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>45805</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 6983-2023</t>
+          <t>A 35734-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44967</v>
+        <v>45147</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>

--- a/Översikt PARTILLE.xlsx
+++ b/Översikt PARTILLE.xlsx
@@ -601,7 +601,7 @@
         <v>45008</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>46050</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46050</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>46279</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 6983-2023</t>
+          <t>A 35734-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44967</v>
+        <v>45147</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1115,7 +1115,7 @@
         <v>45800</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>45800</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>45805</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 35734-2023</t>
+          <t>A 6983-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45147</v>
+        <v>44967</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>

--- a/Översikt PARTILLE.xlsx
+++ b/Översikt PARTILLE.xlsx
@@ -601,7 +601,7 @@
         <v>45008</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>46050</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46050</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>46279</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>45147</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 25251-2025</t>
+          <t>A 6983-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1112,10 +1112,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45800</v>
+        <v>44967</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1127,13 +1127,8 @@
           <t>PARTILLE</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I7" t="n">
-        <v>0.7</v>
+        <v>5.4</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1193,7 +1188,7 @@
         <v>45800</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1271,7 +1266,7 @@
         <v>45805</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1327,7 +1322,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 6983-2023</t>
+          <t>A 25251-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1341,10 +1336,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44967</v>
+        <v>45800</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1356,8 +1351,13 @@
           <t>PARTILLE</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>5.4</v>
+        <v>0.7</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>

--- a/Översikt PARTILLE.xlsx
+++ b/Översikt PARTILLE.xlsx
@@ -601,7 +601,7 @@
         <v>45008</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>46050</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46050</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>46279</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>45147</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 6983-2023</t>
+          <t>A 25251-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1112,10 +1112,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44967</v>
+        <v>45800</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1127,8 +1127,13 @@
           <t>PARTILLE</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I7" t="n">
-        <v>5.4</v>
+        <v>0.7</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1188,7 +1193,7 @@
         <v>45800</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1266,7 +1271,7 @@
         <v>45805</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1322,7 +1327,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 25251-2025</t>
+          <t>A 6983-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1336,10 +1341,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45800</v>
+        <v>44967</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1351,13 +1356,8 @@
           <t>PARTILLE</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>0.7</v>
+        <v>5.4</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>

--- a/Översikt PARTILLE.xlsx
+++ b/Översikt PARTILLE.xlsx
@@ -601,7 +601,7 @@
         <v>45008</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>46050</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46050</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>46279</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 35734-2023</t>
+          <t>A 6983-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45147</v>
+        <v>44967</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1115,7 +1115,7 @@
         <v>45800</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>45800</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>45805</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 6983-2023</t>
+          <t>A 35734-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44967</v>
+        <v>45147</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>

--- a/Översikt PARTILLE.xlsx
+++ b/Översikt PARTILLE.xlsx
@@ -601,7 +601,7 @@
         <v>45008</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>46050</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46050</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>46279</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>44967</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>45800</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>45800</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>45805</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>45147</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>

--- a/Översikt PARTILLE.xlsx
+++ b/Översikt PARTILLE.xlsx
@@ -601,7 +601,7 @@
         <v>45008</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>46050</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46050</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>46279</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>44967</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>45800</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>45800</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>45805</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>45147</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>

--- a/Översikt PARTILLE.xlsx
+++ b/Översikt PARTILLE.xlsx
@@ -601,7 +601,7 @@
         <v>45008</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>46050</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46050</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>46279</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 6983-2023</t>
+          <t>A 35734-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44967</v>
+        <v>45147</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1098,7 +1098,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 25251-2025</t>
+          <t>A 26074-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1112,10 +1112,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45800</v>
+        <v>45805</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1127,13 +1127,8 @@
           <t>PARTILLE</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I7" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1176,7 +1171,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 25254-2025</t>
+          <t>A 25251-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1193,7 +1188,7 @@
         <v>45800</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1211,7 +1206,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1254,7 +1249,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 26074-2025</t>
+          <t>A 6983-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1268,10 +1263,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45805</v>
+        <v>44967</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1284,7 +1279,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.3</v>
+        <v>5.4</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1327,7 +1322,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 35734-2023</t>
+          <t>A 25254-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1341,10 +1336,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45147</v>
+        <v>45800</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1356,8 +1351,13 @@
           <t>PARTILLE</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>5.9</v>
+        <v>0.2</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>

--- a/Översikt PARTILLE.xlsx
+++ b/Översikt PARTILLE.xlsx
@@ -601,7 +601,7 @@
         <v>45008</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>46050</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46050</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>46279</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 35734-2023</t>
+          <t>A 6983-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45147</v>
+        <v>44967</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1098,7 +1098,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 26074-2025</t>
+          <t>A 25254-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1112,10 +1112,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45805</v>
+        <v>45800</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1127,8 +1127,13 @@
           <t>PARTILLE</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I7" t="n">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1171,7 +1176,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 25251-2025</t>
+          <t>A 26074-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1185,10 +1190,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45800</v>
+        <v>45805</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1200,13 +1205,8 @@
           <t>PARTILLE</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I8" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1249,7 +1249,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 6983-2023</t>
+          <t>A 25251-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1263,10 +1263,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44967</v>
+        <v>45800</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1278,8 +1278,13 @@
           <t>PARTILLE</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I9" t="n">
-        <v>5.4</v>
+        <v>0.7</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1322,7 +1327,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 25254-2025</t>
+          <t>A 35734-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1336,10 +1341,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45800</v>
+        <v>45147</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1351,13 +1356,8 @@
           <t>PARTILLE</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>0.2</v>
+        <v>5.9</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>

--- a/Översikt PARTILLE.xlsx
+++ b/Översikt PARTILLE.xlsx
@@ -601,7 +601,7 @@
         <v>45008</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>46050</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46050</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>46279</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 6983-2023</t>
+          <t>A 25251-2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44967</v>
+        <v>45800</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1054,8 +1054,13 @@
           <t>PARTILLE</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I6" t="n">
-        <v>5.4</v>
+        <v>0.7</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1115,7 +1120,7 @@
         <v>45800</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1176,7 +1181,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 26074-2025</t>
+          <t>A 35734-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1190,10 +1195,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45805</v>
+        <v>45147</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1206,7 +1211,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.3</v>
+        <v>5.9</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1249,7 +1254,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 25251-2025</t>
+          <t>A 26074-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1263,10 +1268,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45800</v>
+        <v>45805</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1278,13 +1283,8 @@
           <t>PARTILLE</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I9" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1327,7 +1327,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 35734-2023</t>
+          <t>A 6983-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45147</v>
+        <v>44967</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>

--- a/Översikt PARTILLE.xlsx
+++ b/Översikt PARTILLE.xlsx
@@ -601,7 +601,7 @@
         <v>45008</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>46050</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46050</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>46279</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 25251-2025</t>
+          <t>A 6983-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45800</v>
+        <v>44967</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1054,13 +1054,8 @@
           <t>PARTILLE</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I6" t="n">
-        <v>0.7</v>
+        <v>5.4</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1103,7 +1098,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 25254-2025</t>
+          <t>A 25251-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1120,7 +1115,7 @@
         <v>45800</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1138,7 +1133,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1198,7 +1193,7 @@
         <v>45147</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1254,7 +1249,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 26074-2025</t>
+          <t>A 25254-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1268,10 +1263,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45805</v>
+        <v>45800</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1283,8 +1278,13 @@
           <t>PARTILLE</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I9" t="n">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1327,7 +1327,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 6983-2023</t>
+          <t>A 26074-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44967</v>
+        <v>45805</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>5.4</v>
+        <v>1.3</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>

--- a/Översikt PARTILLE.xlsx
+++ b/Översikt PARTILLE.xlsx
@@ -601,7 +601,7 @@
         <v>45008</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>46050</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46050</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>46279</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 6983-2023</t>
+          <t>A 35734-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44967</v>
+        <v>45147</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1115,7 +1115,7 @@
         <v>45800</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 35734-2023</t>
+          <t>A 6983-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1190,10 +1190,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45147</v>
+        <v>44967</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1266,7 +1266,7 @@
         <v>45800</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>45805</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>

--- a/Översikt PARTILLE.xlsx
+++ b/Översikt PARTILLE.xlsx
@@ -601,7 +601,7 @@
         <v>45008</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>46050</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46050</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>46279</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>45147</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>45800</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>44967</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>45800</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>45805</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>

--- a/Översikt PARTILLE.xlsx
+++ b/Översikt PARTILLE.xlsx
@@ -601,7 +601,7 @@
         <v>45008</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>46050</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46050</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>46279</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>45147</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>45800</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>44967</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>45800</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>45805</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>

--- a/Översikt PARTILLE.xlsx
+++ b/Översikt PARTILLE.xlsx
@@ -601,7 +601,7 @@
         <v>45008</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>46050</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46050</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>46279</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 35734-2023</t>
+          <t>A 25251-2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45147</v>
+        <v>45800</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1054,8 +1054,13 @@
           <t>PARTILLE</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I6" t="n">
-        <v>5.9</v>
+        <v>0.7</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1098,7 +1103,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 25251-2025</t>
+          <t>A 6983-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1112,10 +1117,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45800</v>
+        <v>44967</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1127,13 +1132,8 @@
           <t>PARTILLE</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I7" t="n">
-        <v>0.7</v>
+        <v>5.4</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1176,7 +1176,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 6983-2023</t>
+          <t>A 25254-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1190,10 +1190,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44967</v>
+        <v>45800</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1205,8 +1205,13 @@
           <t>PARTILLE</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I8" t="n">
-        <v>5.4</v>
+        <v>0.2</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1249,7 +1254,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 25254-2025</t>
+          <t>A 26074-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1263,10 +1268,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45800</v>
+        <v>45805</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1278,13 +1283,8 @@
           <t>PARTILLE</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I9" t="n">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1327,7 +1327,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 26074-2025</t>
+          <t>A 35734-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45805</v>
+        <v>45147</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.3</v>
+        <v>5.9</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>

--- a/Översikt PARTILLE.xlsx
+++ b/Översikt PARTILLE.xlsx
@@ -601,7 +601,7 @@
         <v>45008</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>46050</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46050</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>46279</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 25251-2025</t>
+          <t>A 35734-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45800</v>
+        <v>45147</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1054,13 +1054,8 @@
           <t>PARTILLE</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I6" t="n">
-        <v>0.7</v>
+        <v>5.9</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1103,7 +1098,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 6983-2023</t>
+          <t>A 25254-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1117,10 +1112,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44967</v>
+        <v>45800</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1132,8 +1127,13 @@
           <t>PARTILLE</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I7" t="n">
-        <v>5.4</v>
+        <v>0.2</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1176,7 +1176,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 25254-2025</t>
+          <t>A 25251-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1193,7 +1193,7 @@
         <v>45800</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1271,7 +1271,7 @@
         <v>45805</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 35734-2023</t>
+          <t>A 6983-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45147</v>
+        <v>44967</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>

--- a/Översikt PARTILLE.xlsx
+++ b/Översikt PARTILLE.xlsx
@@ -601,7 +601,7 @@
         <v>45008</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>46050</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46050</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>46279</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 35734-2023</t>
+          <t>A 25254-2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45147</v>
+        <v>45800</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1054,8 +1054,13 @@
           <t>PARTILLE</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I6" t="n">
-        <v>5.9</v>
+        <v>0.2</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1098,7 +1103,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 25254-2025</t>
+          <t>A 26074-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1112,10 +1117,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45800</v>
+        <v>45805</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1127,13 +1132,8 @@
           <t>PARTILLE</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I7" t="n">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1176,7 +1176,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 25251-2025</t>
+          <t>A 6983-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1190,10 +1190,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45800</v>
+        <v>44967</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1205,13 +1205,8 @@
           <t>PARTILLE</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I8" t="n">
-        <v>0.7</v>
+        <v>5.4</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1254,7 +1249,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 26074-2025</t>
+          <t>A 25251-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1268,10 +1263,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45805</v>
+        <v>45800</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1283,8 +1278,13 @@
           <t>PARTILLE</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I9" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1327,7 +1327,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 6983-2023</t>
+          <t>A 35734-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44967</v>
+        <v>45147</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>

--- a/Översikt PARTILLE.xlsx
+++ b/Översikt PARTILLE.xlsx
@@ -601,7 +601,7 @@
         <v>45008</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>46050</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46050</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>46279</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>45800</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>45805</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 6983-2023</t>
+          <t>A 35734-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1190,10 +1190,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44967</v>
+        <v>45147</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1266,7 +1266,7 @@
         <v>45800</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 35734-2023</t>
+          <t>A 6983-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45147</v>
+        <v>44967</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>

--- a/Översikt PARTILLE.xlsx
+++ b/Översikt PARTILLE.xlsx
@@ -601,7 +601,7 @@
         <v>45008</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>46050</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46050</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>46279</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 25254-2025</t>
+          <t>A 6983-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45800</v>
+        <v>44967</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1054,13 +1054,8 @@
           <t>PARTILLE</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I6" t="n">
-        <v>0.2</v>
+        <v>5.4</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1103,7 +1098,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 26074-2025</t>
+          <t>A 25251-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1117,10 +1112,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45805</v>
+        <v>45800</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1132,8 +1127,13 @@
           <t>PARTILLE</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I7" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1193,7 +1193,7 @@
         <v>45147</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 25251-2025</t>
+          <t>A 25254-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1266,7 +1266,7 @@
         <v>45800</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1327,7 +1327,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 6983-2023</t>
+          <t>A 26074-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44967</v>
+        <v>45805</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>5.4</v>
+        <v>1.3</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>

--- a/Översikt PARTILLE.xlsx
+++ b/Översikt PARTILLE.xlsx
@@ -601,7 +601,7 @@
         <v>45008</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>46050</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46050</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>46279</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>44967</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>45800</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>45147</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>45800</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>45805</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>

--- a/Översikt PARTILLE.xlsx
+++ b/Översikt PARTILLE.xlsx
@@ -601,7 +601,7 @@
         <v>45008</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>46050</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46050</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>46279</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>44967</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>45800</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>45147</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>45800</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>45805</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>

--- a/Översikt PARTILLE.xlsx
+++ b/Översikt PARTILLE.xlsx
@@ -601,7 +601,7 @@
         <v>45008</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>46050</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46050</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>46279</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 6983-2023</t>
+          <t>A 35734-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44967</v>
+        <v>45147</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1115,7 +1115,7 @@
         <v>45800</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 35734-2023</t>
+          <t>A 6983-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1190,10 +1190,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45147</v>
+        <v>44967</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1266,7 +1266,7 @@
         <v>45800</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>45805</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>

--- a/Översikt PARTILLE.xlsx
+++ b/Översikt PARTILLE.xlsx
@@ -601,7 +601,7 @@
         <v>45008</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>46050</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46050</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>46279</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 35734-2023</t>
+          <t>A 6983-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45147</v>
+        <v>44967</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1098,7 +1098,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 25251-2025</t>
+          <t>A 25254-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1115,7 +1115,7 @@
         <v>45800</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1176,7 +1176,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 6983-2023</t>
+          <t>A 26074-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1190,10 +1190,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44967</v>
+        <v>45805</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>5.4</v>
+        <v>1.3</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1249,7 +1249,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 25254-2025</t>
+          <t>A 25251-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1266,7 +1266,7 @@
         <v>45800</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1327,7 +1327,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 26074-2025</t>
+          <t>A 35734-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45805</v>
+        <v>45147</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.3</v>
+        <v>5.9</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>

--- a/Översikt PARTILLE.xlsx
+++ b/Översikt PARTILLE.xlsx
@@ -601,7 +601,7 @@
         <v>45008</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>46050</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46050</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>46279</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 6983-2023</t>
+          <t>A 35734-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44967</v>
+        <v>45147</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1098,7 +1098,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 25254-2025</t>
+          <t>A 25251-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1115,7 +1115,7 @@
         <v>45800</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1176,7 +1176,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 26074-2025</t>
+          <t>A 25254-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1190,10 +1190,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45805</v>
+        <v>45800</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1205,8 +1205,13 @@
           <t>PARTILLE</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I8" t="n">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1249,7 +1254,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 25251-2025</t>
+          <t>A 26074-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1263,10 +1268,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45800</v>
+        <v>45805</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1278,13 +1283,8 @@
           <t>PARTILLE</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I9" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1327,7 +1327,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 35734-2023</t>
+          <t>A 6983-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45147</v>
+        <v>44967</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>

--- a/Översikt PARTILLE.xlsx
+++ b/Översikt PARTILLE.xlsx
@@ -601,7 +601,7 @@
         <v>45008</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>46050</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46050</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>46279</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>45147</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 25251-2025</t>
+          <t>A 25254-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1115,7 +1115,7 @@
         <v>45800</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1176,7 +1176,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 25254-2025</t>
+          <t>A 26074-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1190,10 +1190,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45800</v>
+        <v>45805</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1205,13 +1205,8 @@
           <t>PARTILLE</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I8" t="n">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1254,7 +1249,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 26074-2025</t>
+          <t>A 6983-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1268,10 +1263,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45805</v>
+        <v>44967</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1284,7 +1279,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.3</v>
+        <v>5.4</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1327,7 +1322,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 6983-2023</t>
+          <t>A 25251-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1341,10 +1336,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44967</v>
+        <v>45800</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1356,8 +1351,13 @@
           <t>PARTILLE</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>5.4</v>
+        <v>0.7</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>

--- a/Översikt PARTILLE.xlsx
+++ b/Översikt PARTILLE.xlsx
@@ -601,7 +601,7 @@
         <v>45008</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>46050</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46050</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>46279</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 35734-2023</t>
+          <t>A 25251-2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45147</v>
+        <v>45800</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1054,8 +1054,13 @@
           <t>PARTILLE</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I6" t="n">
-        <v>5.9</v>
+        <v>0.7</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1098,7 +1103,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 25254-2025</t>
+          <t>A 6983-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1112,10 +1117,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45800</v>
+        <v>44967</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1127,13 +1132,8 @@
           <t>PARTILLE</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I7" t="n">
-        <v>0.2</v>
+        <v>5.4</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1176,7 +1176,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 26074-2025</t>
+          <t>A 35734-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1190,10 +1190,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45805</v>
+        <v>45147</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.3</v>
+        <v>5.9</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1249,7 +1249,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 6983-2023</t>
+          <t>A 25254-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1263,10 +1263,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44967</v>
+        <v>45800</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1278,8 +1278,13 @@
           <t>PARTILLE</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I9" t="n">
-        <v>5.4</v>
+        <v>0.2</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1322,7 +1327,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 25251-2025</t>
+          <t>A 26074-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1336,10 +1341,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45800</v>
+        <v>45805</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1351,13 +1356,8 @@
           <t>PARTILLE</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>

--- a/Översikt PARTILLE.xlsx
+++ b/Översikt PARTILLE.xlsx
@@ -601,7 +601,7 @@
         <v>45008</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>46050</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46050</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>46279</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>45800</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>44967</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>45147</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>45800</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>45805</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>

--- a/Översikt PARTILLE.xlsx
+++ b/Översikt PARTILLE.xlsx
@@ -601,7 +601,7 @@
         <v>45008</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>46050</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46050</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>46279</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>45800</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>44967</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>45147</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>45800</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>45805</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>

--- a/Översikt PARTILLE.xlsx
+++ b/Översikt PARTILLE.xlsx
@@ -601,7 +601,7 @@
         <v>45008</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>46050</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46050</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>46279</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>45800</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>44967</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 35734-2023</t>
+          <t>A 25254-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1190,10 +1190,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45147</v>
+        <v>45800</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1205,8 +1205,13 @@
           <t>PARTILLE</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I8" t="n">
-        <v>5.9</v>
+        <v>0.2</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1249,7 +1254,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 25254-2025</t>
+          <t>A 26074-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1263,10 +1268,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45800</v>
+        <v>45805</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1278,13 +1283,8 @@
           <t>PARTILLE</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I9" t="n">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1327,7 +1327,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 26074-2025</t>
+          <t>A 35734-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45805</v>
+        <v>45147</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.3</v>
+        <v>5.9</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>

--- a/Översikt PARTILLE.xlsx
+++ b/Översikt PARTILLE.xlsx
@@ -601,7 +601,7 @@
         <v>45008</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>46050</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46050</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>46279</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 25251-2025</t>
+          <t>A 6983-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45800</v>
+        <v>44967</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1054,13 +1054,8 @@
           <t>PARTILLE</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I6" t="n">
-        <v>0.7</v>
+        <v>5.4</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1103,7 +1098,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 6983-2023</t>
+          <t>A 25251-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1117,10 +1112,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44967</v>
+        <v>45800</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1132,8 +1127,13 @@
           <t>PARTILLE</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I7" t="n">
-        <v>5.4</v>
+        <v>0.7</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1176,7 +1176,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 25254-2025</t>
+          <t>A 35734-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1190,10 +1190,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45800</v>
+        <v>45147</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1205,13 +1205,8 @@
           <t>PARTILLE</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I8" t="n">
-        <v>0.2</v>
+        <v>5.9</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1254,7 +1249,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 26074-2025</t>
+          <t>A 25254-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1268,10 +1263,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45805</v>
+        <v>45800</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1283,8 +1278,13 @@
           <t>PARTILLE</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I9" t="n">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1327,7 +1327,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 35734-2023</t>
+          <t>A 26074-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45147</v>
+        <v>45805</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>5.9</v>
+        <v>1.3</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>

--- a/Översikt PARTILLE.xlsx
+++ b/Översikt PARTILLE.xlsx
@@ -601,7 +601,7 @@
         <v>45008</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>46050</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46050</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>46279</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 6983-2023</t>
+          <t>A 25254-2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44967</v>
+        <v>45800</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1054,8 +1054,13 @@
           <t>PARTILLE</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I6" t="n">
-        <v>5.4</v>
+        <v>0.2</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1098,7 +1103,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 25251-2025</t>
+          <t>A 26074-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1112,10 +1117,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45800</v>
+        <v>45805</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1127,13 +1132,8 @@
           <t>PARTILLE</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I7" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1176,7 +1176,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 35734-2023</t>
+          <t>A 25251-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1190,10 +1190,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45147</v>
+        <v>45800</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1205,8 +1205,13 @@
           <t>PARTILLE</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I8" t="n">
-        <v>5.9</v>
+        <v>0.7</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1249,7 +1254,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 25254-2025</t>
+          <t>A 35734-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1263,10 +1268,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45800</v>
+        <v>45147</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1278,13 +1283,8 @@
           <t>PARTILLE</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I9" t="n">
-        <v>0.2</v>
+        <v>5.9</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1327,7 +1327,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 26074-2025</t>
+          <t>A 6983-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45805</v>
+        <v>44967</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.3</v>
+        <v>5.4</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>

--- a/Översikt PARTILLE.xlsx
+++ b/Översikt PARTILLE.xlsx
@@ -601,7 +601,7 @@
         <v>45008</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>46050</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>46050</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>46279</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 25254-2025</t>
+          <t>A 6983-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45800</v>
+        <v>44967</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1054,13 +1054,8 @@
           <t>PARTILLE</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I6" t="n">
-        <v>0.2</v>
+        <v>5.4</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1103,7 +1098,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 26074-2025</t>
+          <t>A 25254-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1117,10 +1112,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45805</v>
+        <v>45800</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1132,8 +1127,13 @@
           <t>PARTILLE</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I7" t="n">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1176,7 +1176,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 25251-2025</t>
+          <t>A 26074-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1190,10 +1190,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45800</v>
+        <v>45805</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1205,13 +1205,8 @@
           <t>PARTILLE</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I8" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1254,7 +1249,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 35734-2023</t>
+          <t>A 25251-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1268,10 +1263,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45147</v>
+        <v>45800</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1283,8 +1278,13 @@
           <t>PARTILLE</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I9" t="n">
-        <v>5.9</v>
+        <v>0.7</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1327,7 +1327,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 6983-2023</t>
+          <t>A 35734-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44967</v>
+        <v>45147</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
